--- a/fpa_variance_analysis.xlsx
+++ b/fpa_variance_analysis.xlsx
@@ -17781,7 +17781,7 @@
       </c>
       <c r="F8" s="16" t="inlineStr">
         <is>
-          <t>Opex: Marketing in Customer Support was 48% over budget; 42% above trend forecast in February 2026. Driver: pending analyst review — no known one-off cause on file.</t>
+          <t>Opex: Marketing in Customer Support was 48% over budget; 42% above trend forecast in February 2026. Driver: pending analyst review - no known one-off cause on file.</t>
         </is>
       </c>
     </row>
@@ -17811,7 +17811,7 @@
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
-          <t>Opex: Marketing in Enterprise Services was 47% under budget; 47% below trend forecast in February 2026. Driver: pending analyst review — no known one-off cause on file.</t>
+          <t>Opex: Marketing in Enterprise Services was 47% under budget; 47% below trend forecast in February 2026. Driver: pending analyst review - no known one-off cause on file.</t>
         </is>
       </c>
     </row>
@@ -17841,7 +17841,7 @@
       </c>
       <c r="F10" s="16" t="inlineStr">
         <is>
-          <t>Opex: Marketing in Logistics was 34% over budget in June 2026. Driver: pending analyst review — no known one-off cause on file.</t>
+          <t>Opex: Marketing in Logistics was 34% over budget in June 2026. Driver: pending analyst review - no known one-off cause on file.</t>
         </is>
       </c>
     </row>
@@ -17871,7 +17871,7 @@
       </c>
       <c r="F11" s="16" t="inlineStr">
         <is>
-          <t>Opex: Marketing in Enterprise Services was 34% over budget in April 2025. Driver: pending analyst review — no known one-off cause on file.</t>
+          <t>Opex: Marketing in Enterprise Services was 34% over budget in April 2025. Driver: pending analyst review - no known one-off cause on file.</t>
         </is>
       </c>
     </row>
@@ -17901,7 +17901,7 @@
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
-          <t>Opex: Marketing in Customer Support was 33% under budget in July 2025. Driver: pending analyst review — no known one-off cause on file.</t>
+          <t>Opex: Marketing in Customer Support was 33% under budget in July 2025. Driver: pending analyst review - no known one-off cause on file.</t>
         </is>
       </c>
     </row>
@@ -17931,7 +17931,7 @@
       </c>
       <c r="F13" s="16" t="inlineStr">
         <is>
-          <t>Opex: Marketing in Digital Products was 30% over budget; 30% above trend forecast in April 2026. Driver: pending analyst review — no known one-off cause on file.</t>
+          <t>Opex: Marketing in Digital Products was 30% over budget; 30% above trend forecast in April 2026. Driver: pending analyst review - no known one-off cause on file.</t>
         </is>
       </c>
     </row>
@@ -17961,7 +17961,7 @@
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
-          <t>Opex: Marketing in Customer Support was 42% above trend forecast in October 2025. Driver: pending analyst review — no known one-off cause on file.</t>
+          <t>Opex: Marketing in Customer Support was 42% above trend forecast in October 2025. Driver: pending analyst review - no known one-off cause on file.</t>
         </is>
       </c>
     </row>
@@ -17991,7 +17991,7 @@
       </c>
       <c r="F15" s="16" t="inlineStr">
         <is>
-          <t>Opex: Marketing in Enterprise Services was 43% above trend forecast in June 2026. Driver: pending analyst review — no known one-off cause on file.</t>
+          <t>Opex: Marketing in Enterprise Services was 43% above trend forecast in June 2026. Driver: pending analyst review - no known one-off cause on file.</t>
         </is>
       </c>
     </row>
@@ -18021,7 +18021,7 @@
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
-          <t>Opex: Other in Retail Sales was 25% under budget in June 2025. Driver: pending analyst review — no known one-off cause on file.</t>
+          <t>Opex: Other in Retail Sales was 25% under budget in June 2025. Driver: pending analyst review - no known one-off cause on file.</t>
         </is>
       </c>
     </row>
@@ -18051,7 +18051,7 @@
       </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
-          <t>Opex: Marketing in Customer Support was 52% above trend forecast in September 2025. Driver: pending analyst review — no known one-off cause on file.</t>
+          <t>Opex: Marketing in Customer Support was 52% above trend forecast in September 2025. Driver: pending analyst review - no known one-off cause on file.</t>
         </is>
       </c>
     </row>
@@ -18081,7 +18081,7 @@
       </c>
       <c r="F18" s="16" t="inlineStr">
         <is>
-          <t>Opex: Marketing in Retail Sales was 31% below trend forecast in December 2025. Driver: pending analyst review — no known one-off cause on file.</t>
+          <t>Opex: Marketing in Retail Sales was 31% below trend forecast in December 2025. Driver: pending analyst review - no known one-off cause on file.</t>
         </is>
       </c>
     </row>
@@ -18111,7 +18111,7 @@
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
-          <t>Opex: Other in Retail Sales was 19% under budget; 19% below trend forecast in November 2025. Driver: pending analyst review — no known one-off cause on file.</t>
+          <t>Opex: Other in Retail Sales was 19% under budget; 19% below trend forecast in November 2025. Driver: pending analyst review - no known one-off cause on file.</t>
         </is>
       </c>
     </row>
@@ -18141,7 +18141,7 @@
       </c>
       <c r="F20" s="16" t="inlineStr">
         <is>
-          <t>Opex: Marketing in Retail Sales was 34% above trend forecast in March 2026. Driver: pending analyst review — no known one-off cause on file.</t>
+          <t>Opex: Marketing in Retail Sales was 34% above trend forecast in March 2026. Driver: pending analyst review - no known one-off cause on file.</t>
         </is>
       </c>
     </row>
@@ -18171,7 +18171,7 @@
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
-          <t>Opex: Other in Retail Sales was 17% over budget in May 2025. Driver: pending analyst review — no known one-off cause on file.</t>
+          <t>Opex: Other in Retail Sales was 17% over budget in May 2025. Driver: pending analyst review - no known one-off cause on file.</t>
         </is>
       </c>
     </row>
@@ -18201,7 +18201,7 @@
       </c>
       <c r="F22" s="16" t="inlineStr">
         <is>
-          <t>Opex: Other in Retail Sales was 23% above trend forecast in February 2026. Driver: pending analyst review — no known one-off cause on file.</t>
+          <t>Opex: Other in Retail Sales was 23% above trend forecast in February 2026. Driver: pending analyst review - no known one-off cause on file.</t>
         </is>
       </c>
     </row>
@@ -18231,7 +18231,7 @@
       </c>
       <c r="F23" s="16" t="inlineStr">
         <is>
-          <t>Headcount Cost in Digital Products was 15% over budget; 14% above trend forecast in March 2026. Driver: pending analyst review — no known one-off cause on file.</t>
+          <t>Headcount Cost in Digital Products was 15% over budget; 14% above trend forecast in March 2026. Driver: pending analyst review - no known one-off cause on file.</t>
         </is>
       </c>
     </row>
@@ -18261,7 +18261,7 @@
       </c>
       <c r="F24" s="16" t="inlineStr">
         <is>
-          <t>Opex: Other in Logistics was 22% below trend forecast in August 2025. Driver: pending analyst review — no known one-off cause on file.</t>
+          <t>Opex: Other in Logistics was 22% below trend forecast in August 2025. Driver: pending analyst review - no known one-off cause on file.</t>
         </is>
       </c>
     </row>
@@ -18291,7 +18291,7 @@
       </c>
       <c r="F25" s="16" t="inlineStr">
         <is>
-          <t>Revenue in Digital Products was 15% over budget; 22% above trend forecast in September 2025. Driver: pending analyst review — no known one-off cause on file.</t>
+          <t>Revenue in Digital Products was 15% over budget; 22% above trend forecast in September 2025. Driver: pending analyst review - no known one-off cause on file.</t>
         </is>
       </c>
     </row>
@@ -18321,7 +18321,7 @@
       </c>
       <c r="F26" s="16" t="inlineStr">
         <is>
-          <t>Revenue in Enterprise Services was 14% over budget; 18% above trend forecast in August 2025. Driver: pending analyst review — no known one-off cause on file.</t>
+          <t>Revenue in Enterprise Services was 14% over budget; 18% above trend forecast in August 2025. Driver: pending analyst review - no known one-off cause on file.</t>
         </is>
       </c>
     </row>
@@ -18351,7 +18351,7 @@
       </c>
       <c r="F27" s="16" t="inlineStr">
         <is>
-          <t>Opex: Other in Logistics was 21% above trend forecast in September 2026. Driver: pending analyst review — no known one-off cause on file.</t>
+          <t>Opex: Other in Logistics was 21% above trend forecast in September 2026. Driver: pending analyst review - no known one-off cause on file.</t>
         </is>
       </c>
     </row>
@@ -18381,7 +18381,7 @@
       </c>
       <c r="F28" s="16" t="inlineStr">
         <is>
-          <t>Revenue in Digital Products was 13% over budget; 14% above trend forecast in September 2026. Driver: pending analyst review — no known one-off cause on file.</t>
+          <t>Revenue in Digital Products was 13% over budget; 14% above trend forecast in September 2026. Driver: pending analyst review - no known one-off cause on file.</t>
         </is>
       </c>
     </row>
@@ -18411,7 +18411,7 @@
       </c>
       <c r="F29" s="16" t="inlineStr">
         <is>
-          <t>Opex: Marketing in Retail Sales was 32% above trend forecast in August 2025. Driver: pending analyst review — no known one-off cause on file.</t>
+          <t>Opex: Marketing in Retail Sales was 32% above trend forecast in August 2025. Driver: pending analyst review - no known one-off cause on file.</t>
         </is>
       </c>
     </row>
@@ -18441,7 +18441,7 @@
       </c>
       <c r="F30" s="16" t="inlineStr">
         <is>
-          <t>Revenue in Customer Support was 12% under budget in February 2026. Driver: pending analyst review — no known one-off cause on file.</t>
+          <t>Revenue in Customer Support was 12% under budget in February 2026. Driver: pending analyst review - no known one-off cause on file.</t>
         </is>
       </c>
     </row>
@@ -18471,7 +18471,7 @@
       </c>
       <c r="F31" s="16" t="inlineStr">
         <is>
-          <t>Revenue in Digital Products was 12% under budget in June 2025. Driver: pending analyst review — no known one-off cause on file.</t>
+          <t>Revenue in Digital Products was 12% under budget in June 2025. Driver: pending analyst review - no known one-off cause on file.</t>
         </is>
       </c>
     </row>
@@ -18501,7 +18501,7 @@
       </c>
       <c r="F32" s="16" t="inlineStr">
         <is>
-          <t>Revenue in Retail Sales was 11% under budget in May 2026. Driver: pending analyst review — no known one-off cause on file.</t>
+          <t>Revenue in Retail Sales was 11% under budget in May 2026. Driver: pending analyst review - no known one-off cause on file.</t>
         </is>
       </c>
     </row>
@@ -18531,7 +18531,7 @@
       </c>
       <c r="F33" s="16" t="inlineStr">
         <is>
-          <t>Revenue in Enterprise Services was 11% under budget; 13% below trend forecast in September 2025. Driver: pending analyst review — no known one-off cause on file.</t>
+          <t>Revenue in Enterprise Services was 11% under budget; 13% below trend forecast in September 2025. Driver: pending analyst review - no known one-off cause on file.</t>
         </is>
       </c>
     </row>
@@ -18561,7 +18561,7 @@
       </c>
       <c r="F34" s="16" t="inlineStr">
         <is>
-          <t>COGS in Enterprise Services was 11% over budget in April 2025. Driver: pending analyst review — no known one-off cause on file.</t>
+          <t>COGS in Enterprise Services was 11% over budget in April 2025. Driver: pending analyst review - no known one-off cause on file.</t>
         </is>
       </c>
     </row>
@@ -18591,7 +18591,7 @@
       </c>
       <c r="F35" s="16" t="inlineStr">
         <is>
-          <t>Opex: Other in Retail Sales was 17% above trend forecast in June 2026. Driver: pending analyst review — no known one-off cause on file.</t>
+          <t>Opex: Other in Retail Sales was 17% above trend forecast in June 2026. Driver: pending analyst review - no known one-off cause on file.</t>
         </is>
       </c>
     </row>
@@ -18621,7 +18621,7 @@
       </c>
       <c r="F36" s="16" t="inlineStr">
         <is>
-          <t>COGS in Enterprise Services was 10% under budget in June 2025. Driver: pending analyst review — no known one-off cause on file.</t>
+          <t>COGS in Enterprise Services was 10% under budget in June 2025. Driver: pending analyst review - no known one-off cause on file.</t>
         </is>
       </c>
     </row>
@@ -18651,7 +18651,7 @@
       </c>
       <c r="F37" s="16" t="inlineStr">
         <is>
-          <t>COGS in Customer Support was 10% over budget; 17% above trend forecast in February 2026. Driver: pending analyst review — no known one-off cause on file.</t>
+          <t>COGS in Customer Support was 10% over budget; 17% above trend forecast in February 2026. Driver: pending analyst review - no known one-off cause on file.</t>
         </is>
       </c>
     </row>
@@ -18681,7 +18681,7 @@
       </c>
       <c r="F38" s="16" t="inlineStr">
         <is>
-          <t>Opex: Other in Digital Products was 20% above trend forecast in March 2026. Driver: pending analyst review — no known one-off cause on file.</t>
+          <t>Opex: Other in Digital Products was 20% above trend forecast in March 2026. Driver: pending analyst review - no known one-off cause on file.</t>
         </is>
       </c>
     </row>
@@ -18711,7 +18711,7 @@
       </c>
       <c r="F39" s="16" t="inlineStr">
         <is>
-          <t>COGS in Retail Sales was 9% over budget; 14% above trend forecast in May 2026. Driver: pending analyst review — no known one-off cause on file.</t>
+          <t>COGS in Retail Sales was 9% over budget; 14% above trend forecast in May 2026. Driver: pending analyst review - no known one-off cause on file.</t>
         </is>
       </c>
     </row>
@@ -18741,7 +18741,7 @@
       </c>
       <c r="F40" s="16" t="inlineStr">
         <is>
-          <t>COGS in Enterprise Services was 9% over budget; 13% above trend forecast in June 2026. Driver: pending analyst review — no known one-off cause on file.</t>
+          <t>COGS in Enterprise Services was 9% over budget; 13% above trend forecast in June 2026. Driver: pending analyst review - no known one-off cause on file.</t>
         </is>
       </c>
     </row>
@@ -18771,7 +18771,7 @@
       </c>
       <c r="F41" s="16" t="inlineStr">
         <is>
-          <t>Headcount Cost in Enterprise Services was 8% over budget; 10% above trend forecast in September 2026. Driver: pending analyst review — no known one-off cause on file.</t>
+          <t>Headcount Cost in Enterprise Services was 8% over budget; 10% above trend forecast in September 2026. Driver: pending analyst review - no known one-off cause on file.</t>
         </is>
       </c>
     </row>
@@ -18801,7 +18801,7 @@
       </c>
       <c r="F42" s="16" t="inlineStr">
         <is>
-          <t>Revenue in Customer Support was 12% below trend forecast in September 2025. Driver: pending analyst review — no known one-off cause on file.</t>
+          <t>Revenue in Customer Support was 12% below trend forecast in September 2025. Driver: pending analyst review - no known one-off cause on file.</t>
         </is>
       </c>
     </row>
@@ -18831,7 +18831,7 @@
       </c>
       <c r="F43" s="16" t="inlineStr">
         <is>
-          <t>Headcount Cost in Logistics was 8% over budget; 8% above trend forecast in October 2025. Driver: pending analyst review — no known one-off cause on file.</t>
+          <t>Headcount Cost in Logistics was 8% over budget; 8% above trend forecast in October 2025. Driver: pending analyst review - no known one-off cause on file.</t>
         </is>
       </c>
     </row>
@@ -18861,7 +18861,7 @@
       </c>
       <c r="F44" s="16" t="inlineStr">
         <is>
-          <t>Headcount Cost in Logistics was 8% under budget in September 2026. Driver: pending analyst review — no known one-off cause on file.</t>
+          <t>Headcount Cost in Logistics was 8% under budget in September 2026. Driver: pending analyst review - no known one-off cause on file.</t>
         </is>
       </c>
     </row>
@@ -18891,7 +18891,7 @@
       </c>
       <c r="F45" s="16" t="inlineStr">
         <is>
-          <t>COGS in Digital Products was 12% above trend forecast in January 2026. Driver: pending analyst review — no known one-off cause on file.</t>
+          <t>COGS in Digital Products was 12% above trend forecast in January 2026. Driver: pending analyst review - no known one-off cause on file.</t>
         </is>
       </c>
     </row>
@@ -18921,7 +18921,7 @@
       </c>
       <c r="F46" s="16" t="inlineStr">
         <is>
-          <t>Headcount Cost in Retail Sales was 8% over budget; 10% above trend forecast in August 2026. Driver: pending analyst review — no known one-off cause on file.</t>
+          <t>Headcount Cost in Retail Sales was 8% over budget; 10% above trend forecast in August 2026. Driver: pending analyst review - no known one-off cause on file.</t>
         </is>
       </c>
     </row>
@@ -18951,7 +18951,7 @@
       </c>
       <c r="F47" s="16" t="inlineStr">
         <is>
-          <t>COGS in Logistics was 10% above trend forecast in January 2026. Driver: pending analyst review — no known one-off cause on file.</t>
+          <t>COGS in Logistics was 10% above trend forecast in January 2026. Driver: pending analyst review - no known one-off cause on file.</t>
         </is>
       </c>
     </row>
@@ -18981,7 +18981,7 @@
       </c>
       <c r="F48" s="16" t="inlineStr">
         <is>
-          <t>Opex: Salaries in Logistics was 7% under budget in August 2025. Driver: pending analyst review — no known one-off cause on file.</t>
+          <t>Opex: Salaries in Logistics was 7% under budget in August 2025. Driver: pending analyst review - no known one-off cause on file.</t>
         </is>
       </c>
     </row>
@@ -19011,7 +19011,7 @@
       </c>
       <c r="F49" s="16" t="inlineStr">
         <is>
-          <t>Opex: Salaries in Digital Products was 7% over budget; 8% above trend forecast in September 2026. Driver: pending analyst review — no known one-off cause on file.</t>
+          <t>Opex: Salaries in Digital Products was 7% over budget; 8% above trend forecast in September 2026. Driver: pending analyst review - no known one-off cause on file.</t>
         </is>
       </c>
     </row>
@@ -19041,7 +19041,7 @@
       </c>
       <c r="F50" s="16" t="inlineStr">
         <is>
-          <t>Opex: Salaries in Enterprise Services was 7% below trend forecast in July 2026. Driver: pending analyst review — no known one-off cause on file.</t>
+          <t>Opex: Salaries in Enterprise Services was 7% below trend forecast in July 2026. Driver: pending analyst review - no known one-off cause on file.</t>
         </is>
       </c>
     </row>
@@ -19071,7 +19071,7 @@
       </c>
       <c r="F51" s="16" t="inlineStr">
         <is>
-          <t>COGS in Digital Products was 9% above trend forecast in July 2026. Driver: pending analyst review — no known one-off cause on file.</t>
+          <t>COGS in Digital Products was 9% above trend forecast in July 2026. Driver: pending analyst review - no known one-off cause on file.</t>
         </is>
       </c>
     </row>
@@ -19101,7 +19101,7 @@
       </c>
       <c r="F52" s="16" t="inlineStr">
         <is>
-          <t>Revenue in Enterprise Services was 12% above trend forecast in January 2026. Driver: pending analyst review — no known one-off cause on file.</t>
+          <t>Revenue in Enterprise Services was 12% above trend forecast in January 2026. Driver: pending analyst review - no known one-off cause on file.</t>
         </is>
       </c>
     </row>
@@ -19131,7 +19131,7 @@
       </c>
       <c r="F53" s="16" t="inlineStr">
         <is>
-          <t>Revenue in Logistics was 11% above trend forecast in February 2026. Driver: pending analyst review — no known one-off cause on file.</t>
+          <t>Revenue in Logistics was 11% above trend forecast in February 2026. Driver: pending analyst review - no known one-off cause on file.</t>
         </is>
       </c>
     </row>
@@ -19161,7 +19161,7 @@
       </c>
       <c r="F54" s="16" t="inlineStr">
         <is>
-          <t>Headcount Cost in Digital Products was 8% below trend forecast in October 2025. Driver: pending analyst review — no known one-off cause on file.</t>
+          <t>Headcount Cost in Digital Products was 8% below trend forecast in October 2025. Driver: pending analyst review - no known one-off cause on file.</t>
         </is>
       </c>
     </row>
@@ -19191,7 +19191,7 @@
       </c>
       <c r="F55" s="16" t="inlineStr">
         <is>
-          <t>Revenue in Digital Products was 15% above trend forecast in April 2026. Driver: pending analyst review — no known one-off cause on file.</t>
+          <t>Revenue in Digital Products was 15% above trend forecast in April 2026. Driver: pending analyst review - no known one-off cause on file.</t>
         </is>
       </c>
     </row>
@@ -19221,7 +19221,7 @@
       </c>
       <c r="F56" s="16" t="inlineStr">
         <is>
-          <t>Opex: Salaries in Customer Support was 8% above trend forecast in July 2026. Driver: pending analyst review — no known one-off cause on file.</t>
+          <t>Opex: Salaries in Customer Support was 8% above trend forecast in July 2026. Driver: pending analyst review - no known one-off cause on file.</t>
         </is>
       </c>
     </row>
@@ -19251,7 +19251,7 @@
       </c>
       <c r="F57" s="16" t="inlineStr">
         <is>
-          <t>Revenue in Digital Products was 17% above trend forecast in March 2026. Driver: pending analyst review — no known one-off cause on file.</t>
+          <t>Revenue in Digital Products was 17% above trend forecast in March 2026. Driver: pending analyst review - no known one-off cause on file.</t>
         </is>
       </c>
     </row>
@@ -19281,7 +19281,7 @@
       </c>
       <c r="F58" s="16" t="inlineStr">
         <is>
-          <t>Opex: Salaries in Logistics was 8% above trend forecast in July 2026. Driver: pending analyst review — no known one-off cause on file.</t>
+          <t>Opex: Salaries in Logistics was 8% above trend forecast in July 2026. Driver: pending analyst review - no known one-off cause on file.</t>
         </is>
       </c>
     </row>
@@ -19311,7 +19311,7 @@
       </c>
       <c r="F59" s="16" t="inlineStr">
         <is>
-          <t>COGS in Enterprise Services was 11% above trend forecast in September 2025. Driver: pending analyst review — no known one-off cause on file.</t>
+          <t>COGS in Enterprise Services was 11% above trend forecast in September 2025. Driver: pending analyst review - no known one-off cause on file.</t>
         </is>
       </c>
     </row>
@@ -19341,7 +19341,7 @@
       </c>
       <c r="F60" s="16" t="inlineStr">
         <is>
-          <t>Opex: Salaries in Customer Support was 11% below trend forecast in February 2026. Driver: pending analyst review — no known one-off cause on file.</t>
+          <t>Opex: Salaries in Customer Support was 11% below trend forecast in February 2026. Driver: pending analyst review - no known one-off cause on file.</t>
         </is>
       </c>
     </row>
@@ -19371,7 +19371,7 @@
       </c>
       <c r="F61" s="16" t="inlineStr">
         <is>
-          <t>Revenue in Customer Support was 14% above trend forecast in May 2026. Driver: pending analyst review — no known one-off cause on file.</t>
+          <t>Revenue in Customer Support was 14% above trend forecast in May 2026. Driver: pending analyst review - no known one-off cause on file.</t>
         </is>
       </c>
     </row>
@@ -19401,7 +19401,7 @@
       </c>
       <c r="F62" s="16" t="inlineStr">
         <is>
-          <t>Opex: Salaries in Customer Support was 9% below trend forecast in April 2026. Driver: pending analyst review — no known one-off cause on file.</t>
+          <t>Opex: Salaries in Customer Support was 9% below trend forecast in April 2026. Driver: pending analyst review - no known one-off cause on file.</t>
         </is>
       </c>
     </row>
@@ -19431,7 +19431,7 @@
       </c>
       <c r="F63" s="16" t="inlineStr">
         <is>
-          <t>Opex: Other in Logistics was 20% below trend forecast in December 2025. Driver: pending analyst review — no known one-off cause on file.</t>
+          <t>Opex: Other in Logistics was 20% below trend forecast in December 2025. Driver: pending analyst review - no known one-off cause on file.</t>
         </is>
       </c>
     </row>
@@ -19461,7 +19461,7 @@
       </c>
       <c r="F64" s="16" t="inlineStr">
         <is>
-          <t>Headcount Cost in Enterprise Services was 13% above trend forecast in July 2026. Driver: pending analyst review — no known one-off cause on file.</t>
+          <t>Headcount Cost in Enterprise Services was 13% above trend forecast in July 2026. Driver: pending analyst review - no known one-off cause on file.</t>
         </is>
       </c>
     </row>
@@ -19491,7 +19491,7 @@
       </c>
       <c r="F65" s="16" t="inlineStr">
         <is>
-          <t>COGS in Digital Products was 9% above trend forecast in November 2025. Driver: pending analyst review — no known one-off cause on file.</t>
+          <t>COGS in Digital Products was 9% above trend forecast in November 2025. Driver: pending analyst review - no known one-off cause on file.</t>
         </is>
       </c>
     </row>
@@ -19521,7 +19521,7 @@
       </c>
       <c r="F66" s="16" t="inlineStr">
         <is>
-          <t>Revenue in Customer Support was 11% above trend forecast in December 2025. Driver: pending analyst review — no known one-off cause on file.</t>
+          <t>Revenue in Customer Support was 11% above trend forecast in December 2025. Driver: pending analyst review - no known one-off cause on file.</t>
         </is>
       </c>
     </row>
@@ -19551,7 +19551,7 @@
       </c>
       <c r="F67" s="16" t="inlineStr">
         <is>
-          <t>Revenue in Retail Sales was 11% above trend forecast in September 2026. Driver: pending analyst review — no known one-off cause on file.</t>
+          <t>Revenue in Retail Sales was 11% above trend forecast in September 2026. Driver: pending analyst review - no known one-off cause on file.</t>
         </is>
       </c>
     </row>
@@ -19581,7 +19581,7 @@
       </c>
       <c r="F68" s="16" t="inlineStr">
         <is>
-          <t>Opex: Salaries in Customer Support was 8% below trend forecast in March 2026. Driver: pending analyst review — no known one-off cause on file.</t>
+          <t>Opex: Salaries in Customer Support was 8% below trend forecast in March 2026. Driver: pending analyst review - no known one-off cause on file.</t>
         </is>
       </c>
     </row>
@@ -19611,7 +19611,7 @@
       </c>
       <c r="F69" s="16" t="inlineStr">
         <is>
-          <t>Headcount Cost in Enterprise Services was 9% above trend forecast in May 2026. Driver: pending analyst review — no known one-off cause on file.</t>
+          <t>Headcount Cost in Enterprise Services was 9% above trend forecast in May 2026. Driver: pending analyst review - no known one-off cause on file.</t>
         </is>
       </c>
     </row>
@@ -19641,7 +19641,7 @@
       </c>
       <c r="F70" s="16" t="inlineStr">
         <is>
-          <t>Headcount Cost in Enterprise Services was 12% above trend forecast in June 2026. Driver: pending analyst review — no known one-off cause on file.</t>
+          <t>Headcount Cost in Enterprise Services was 12% above trend forecast in June 2026. Driver: pending analyst review - no known one-off cause on file.</t>
         </is>
       </c>
     </row>
